--- a/www/ig/fhir/core/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
+    <t>Identifiant de contact dans la ressource Patient
++This extension carries the contact identifier in the patient resource</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -132,7 +134,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>fhirpath:Patient.contact</t>
+    <t>element:Patient.contact</t>
   </si>
   <si>
     <t>ID</t>
@@ -257,9 +259,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -669,42 +668,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,7 +850,7 @@
         <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
         <v>23</v>
@@ -914,10 +913,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -925,10 +924,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -939,25 +938,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1008,13 +1007,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1023,15 +1022,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1054,13 +1053,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1099,19 +1098,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1123,7 +1122,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1131,10 +1130,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1142,10 +1141,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1157,16 +1156,16 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1216,13 +1215,13 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1231,15 +1230,15 @@
         <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1250,7 +1249,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1262,13 +1261,13 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1319,22 +1318,22 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,9 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Identifiant de contact dans la ressource Patient
--This extension carries the contact identifier in the patient resource</t>
+    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -116,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -134,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Patient.contact</t>
+    <t>fhirpath:Patient.contact</t>
   </si>
   <si>
     <t>ID</t>
@@ -259,6 +257,9 @@
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -668,42 +669,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="8.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,7 +851,7 @@
         <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
         <v>23</v>
@@ -913,10 +914,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -924,10 +925,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -938,7 +939,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -950,13 +951,13 @@
         <v>77</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1007,13 +1008,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1022,15 +1023,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1053,13 +1054,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1098,19 +1099,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1122,7 +1123,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1130,10 +1131,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1141,10 +1142,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1156,16 +1157,16 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1215,13 +1216,13 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1230,15 +1231,15 @@
         <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1249,7 +1250,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1261,13 +1262,13 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1318,22 +1319,22 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
+    <t>Identifiant de contact dans la ressource Patient
++This extension carries the contact identifier in the patient resource</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -132,7 +134,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>fhirpath:Patient.contact</t>
+    <t>element:Patient.contact</t>
   </si>
   <si>
     <t>ID</t>
@@ -257,9 +259,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -669,42 +668,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,7 +850,7 @@
         <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
         <v>23</v>
@@ -914,10 +913,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -925,10 +924,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -939,25 +938,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1008,13 +1007,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1023,15 +1022,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1054,13 +1053,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1099,19 +1098,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1123,7 +1122,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1131,10 +1130,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1142,10 +1141,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1157,16 +1156,16 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1216,13 +1215,13 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1231,15 +1230,15 @@
         <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1250,7 +1249,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1262,13 +1261,13 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1319,22 +1318,22 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
